--- a/AAII_Financials/Quarterly/META_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/META_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>META</t>
   </si>
@@ -656,323 +656,335 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="27" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>60801000</v>
+      </c>
+      <c r="E8" s="3">
         <v>56311000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>59893000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>51242000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>47516000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>42314000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>48385000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>40589000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>39071000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>36455000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>40111000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>34146000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>31999000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>28645000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>32165000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>27714000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>28822000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>27908000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>33671000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>29010000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>29077000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>26171000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>28072000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>21470000</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>11330000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10218000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10906000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9206000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8491000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7572000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8839000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7375000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7308000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6640000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7602000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6197000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5987000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6218000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6841000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5716000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5192000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6005000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6348000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5771000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5399000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5131000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5210000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4194000</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>49471000</v>
+      </c>
+      <c r="E10" s="3">
         <v>46093000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>48987000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>42036000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>39025000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>34742000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>39546000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>33214000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>31763000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>29815000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>32509000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>27949000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>26012000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>22427000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>25324000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>21998000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>23630000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>21903000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>27323000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>23239000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>23678000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>21040000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>22862000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>17276000</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -999,82 +1011,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>21656000</v>
+      </c>
+      <c r="E12" s="3">
         <v>17699000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>17135000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>15144000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12942000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12150000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>12180000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>11177000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>10537000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>9978000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>9807000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>9011000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9192000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>8901000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8052000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>9170000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>8690000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7707000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7046000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6316000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6096000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5197000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>5207000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4763000</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1147,31 +1163,34 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>3133000</v>
+      </c>
+      <c r="E14" s="3">
         <v>1075000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-590000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-922000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>511000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-135000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-53000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>10</v>
@@ -1179,23 +1198,23 @@
       <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" s="3">
         <v>1208000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>344000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>184000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>621000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4611000</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>10</v>
@@ -1206,8 +1225,8 @@
       <c r="U14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1215,59 +1234,62 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>10</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6356000</v>
+      </c>
+      <c r="E15" s="3">
         <v>5999000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5411000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4963000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4342000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3900000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4402000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4027000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3637000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3374000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3172000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2859000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2623000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2524000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1295,8 +1317,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1320,156 +1345,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>39626000</v>
+      </c>
+      <c r="E17" s="3">
         <v>33439000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35148000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>30707000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>27075000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>24759000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>25021000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23239000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>24224000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>22637000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>22620000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>20054000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>22423000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20797000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25766000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>22050000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>20464000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>19384000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21086000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18587000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>16710000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>14793000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>15297000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13430000</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>21175000</v>
+      </c>
+      <c r="E18" s="3">
         <v>22872000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>24745000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>20535000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>20441000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>17555000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>23364000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17350000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14847000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13818000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17491000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14092000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9576000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7848000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6399000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5664000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8358000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8524000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>12585000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10423000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>12367000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11378000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>12775000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>8040000</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1496,200 +1528,207 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-638000</v>
+      </c>
+      <c r="E20" s="3">
         <v>227000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>150000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-74000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-364000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-274000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>345000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-19000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>153000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>93000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-72000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>123000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>306000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>58000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-250000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-88000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-172000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>384000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>118000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>142000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>146000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>125000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>280000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>93000</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>28169000</v>
+      </c>
+      <c r="E21" s="3">
         <v>28644000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>30006000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>25572000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>25147000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>21729000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>27421000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>21396000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>18331000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>17099000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>20735000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>16828000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11893000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10314000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8525000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7751000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>10165000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>11064000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>14717000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>12560000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>14499000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>13475000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>14918000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9831000</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>783000</v>
+      </c>
+      <c r="E22" s="3">
         <v>562000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>456000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>227000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>241000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>240000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>251000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>208000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>128000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>127000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>136000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>139000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>116000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>55000</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>10</v>
@@ -1703,11 +1742,11 @@
       <c r="U22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3" t="s">
+      <c r="V22" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>10</v>
@@ -1718,156 +1757,165 @@
       <c r="Z22" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>18756000</v>
+      </c>
+      <c r="E23" s="3">
         <v>21752000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>25354000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21663000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>20534000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>18382000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>23552000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>17822000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>15106000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14183000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>16807000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>14020000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9293000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7307000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6149000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5576000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8186000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8908000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>12703000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>10565000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>12513000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>11503000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>13055000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8133000</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2908000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-5021000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2586000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>18954000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2197000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1738000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2714000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2134000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1641000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1814000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2790000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2437000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1505000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1598000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1135000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1181000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1499000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1443000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2418000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1371000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2119000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2006000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1836000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>287000</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1940,156 +1988,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15848000</v>
+      </c>
+      <c r="E26" s="3">
         <v>26773000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22768000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2709000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>18337000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>16644000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>20838000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15688000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>13465000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>12369000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14017000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11583000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7788000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5709000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5014000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4395000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6687000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7465000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>10285000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>9194000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>10394000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>9497000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>11219000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>7846000</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15848000</v>
+      </c>
+      <c r="E27" s="3">
         <v>26773000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>22768000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2709000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>18337000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>16644000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>20838000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>15688000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>13465000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12369000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>14017000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11583000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7788000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5709000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5014000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4395000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6687000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>7465000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>10285000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>9194000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>10394000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>9497000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>11219000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>7846000</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2162,8 +2219,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2207,13 +2267,13 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-361000</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>10</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>10</v>
@@ -2224,8 +2284,8 @@
       <c r="V29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2236,8 +2296,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2310,8 +2373,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2384,156 +2450,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>638000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-227000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-150000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>74000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>364000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>274000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-345000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>19000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-153000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-93000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>72000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-123000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-306000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-58000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>250000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>88000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>172000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-384000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-118000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-142000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-146000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-125000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-280000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-93000</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15848000</v>
+      </c>
+      <c r="E33" s="3">
         <v>26773000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>22768000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2709000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>18337000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16644000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>20838000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15688000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>13465000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>12369000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>14017000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11583000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7788000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5709000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4653000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4395000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6687000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7465000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>10285000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>9194000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>10394000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>9497000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>11219000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>7846000</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2606,161 +2681,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15848000</v>
+      </c>
+      <c r="E35" s="3">
         <v>26773000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>22768000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2709000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>18337000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16644000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>20838000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15688000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>13465000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>12369000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>14017000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11583000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7788000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5709000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4653000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4395000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6687000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7465000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>10285000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>9194000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>10394000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>9497000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>11219000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>7846000</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2787,8 +2871,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2815,230 +2900,240 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15462000</v>
+      </c>
+      <c r="E41" s="3">
         <v>23426000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>35873000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10187000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12005000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>28750000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>43889000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>43852000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>32045000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>32307000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>41862000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>36890000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>28785000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11551000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>14681000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>14308000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>12681000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>14886000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>16601000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>14496000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>16186000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>19513000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>17576000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11617000</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>74798000</v>
+      </c>
+      <c r="E42" s="3">
         <v>57754000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>45719000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>34261000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>35066000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>41480000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>33926000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>27048000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>26035000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>25813000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>23541000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>24233000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>24661000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>25888000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>26057000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>27468000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>27808000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>29004000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>31397000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>43579000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>47894000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>44706000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>44378000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>44003000</v>
       </c>
     </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>21752000</v>
+      </c>
+      <c r="E43" s="3">
         <v>17470000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>19769000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17297000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16561000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14514000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>16994000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14700000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>14505000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13430000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16169000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12944000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12511000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11044000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13466000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11227000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11525000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11390000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>14039000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>12088000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>11698000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>10276000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>11335000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8024000</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3081,8 +3176,8 @@
       <c r="P44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3111,25 +3206,28 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2030000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1480000</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4660000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3260000</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>10</v>
@@ -3155,334 +3253,349 @@
       <c r="P45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R45" s="3">
         <v>5345000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5312000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3973000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3985000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4629000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5258000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4919000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2827000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2381000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2155000</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>125475000</v>
+      </c>
+      <c r="E46" s="3">
         <v>109765000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>108722000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>73118000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>73613000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>90227000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>100045000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>91067000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>76431000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>75330000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>85365000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>78378000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>69560000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>52483000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>59549000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>58315000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>55987000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>59265000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>66666000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>75421000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>80697000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>77322000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>75670000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>65799000</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>30157000</v>
+      </c>
+      <c r="E47" s="3">
         <v>28410000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>27524000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>25074000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>21988000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6168000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6070000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6071000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6207000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6218000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6141000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6142000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6208000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6167000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6201000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6528000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6536000</v>
-      </c>
-      <c r="T47" s="3">
-        <v>6775000</v>
       </c>
       <c r="U47" s="3">
         <v>6775000</v>
       </c>
       <c r="V47" s="3">
+        <v>6775000</v>
+      </c>
+      <c r="W47" s="3">
         <v>6758000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>6393000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6342000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6234000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6164000</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>249709000</v>
+      </c>
+      <c r="E48" s="3">
         <v>218044000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>196804000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>177642000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>162701000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>149072000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>136268000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>126974000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>117017000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>112463000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>109881000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>104805000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>100904000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>97055000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>92191000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>87379000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>81718000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>73823000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>69964000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>64789000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>61434000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>57922000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>54981000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>51730000</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>23406000</v>
+      </c>
+      <c r="E49" s="3">
         <v>24748000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>28226000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>21158000</v>
-      </c>
-      <c r="G49" s="3">
-        <v>20654000</v>
       </c>
       <c r="H49" s="3">
         <v>20654000</v>
       </c>
       <c r="I49" s="3">
+        <v>20654000</v>
+      </c>
+      <c r="J49" s="3">
         <v>21569000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>21627000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>21638000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>21483000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>21442000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>21481000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>21515000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>21598000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>21203000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>21143000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>21194000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>20833000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>19831000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>19430000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>19733000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>19561000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>19673000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>19775000</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3555,8 +3668,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3629,82 +3745,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>21209000</v>
+      </c>
+      <c r="E52" s="3">
         <v>14283000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4745000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6852000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15788000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14092000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12102000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10669000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8945000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7350000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6794000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5468000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8501000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7188000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6583000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5529000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4344000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3522000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2751000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3187000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2352000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2376000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2758000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2969000</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3777,82 +3899,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>449956000</v>
+      </c>
+      <c r="E54" s="3">
         <v>395250000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>366021000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>303844000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>294744000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>280213000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>276054000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>256408000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>230238000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>222844000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>229623000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>216274000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>206688000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>184491000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>185727000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>178894000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>169779000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>164218000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>165987000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>169585000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>170609000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>163523000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>159316000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>146437000</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3879,8 +4007,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3907,167 +4036,174 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15889000</v>
+      </c>
+      <c r="E57" s="3">
         <v>13326000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8894000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7798000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10271000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8512000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7687000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7656000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3173000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3785000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4849000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4372000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3093000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3672000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6107000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4846000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4990000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4181000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5135000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3104000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1922000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1884000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2424000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1906000</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2425000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2414000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2521000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2113000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1977000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1976000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1942000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2016000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1917000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1676000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1623000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1545000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1577000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1593000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>129000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>64000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>78000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>81000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>75000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>72000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>63000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>53000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>54000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>62000</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="3">
         <v>23270000</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>10</v>
@@ -4075,284 +4211,296 @@
       <c r="H59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J59" s="3">
         <v>17617000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>18200000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17784000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19307000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18829000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19646000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20913000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16724000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>20790000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17777000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17149000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16824000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15925000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14636000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12889000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10780000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>12503000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9976000</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>56379000</v>
+      </c>
+      <c r="E60" s="3">
         <v>46753000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>41836000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>36958000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>37305000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33890000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33596000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>33330000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27004000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28101000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>31960000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30531000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>29921000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>25381000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>27026000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>22687000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>22217000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>21086000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>21135000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>17812000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>14874000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12717000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14981000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11944000</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>109893000</v>
+      </c>
+      <c r="E61" s="3">
         <v>84355000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>82560000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>48947000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>47583000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>47543000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>47118000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>47031000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>36074000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>35957000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>35611000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>35331000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>35401000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>26669000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10481000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10439000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>534000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>524000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>506000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>507000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>493000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>474000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>469000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>466000</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>22463000</v>
+      </c>
+      <c r="E62" s="3">
         <v>20461000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24382000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23873000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>14786000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13751000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12703000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11518000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10397000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9257000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8884000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7539000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7333000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7646000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>22507000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>21674000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>21261000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>19380000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>19467000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>17906000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>17015000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>16675000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>15576000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>16296000</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4425,8 +4573,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4499,8 +4650,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4573,82 +4727,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>188735000</v>
+      </c>
+      <c r="E66" s="3">
         <v>151569000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>148778000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>109778000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>99674000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>95184000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>93417000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>91879000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>73475000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>73315000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>76455000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>73401000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>72655000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>59696000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>60014000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>54800000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>44012000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>40990000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>41108000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>36225000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>32382000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>29866000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>31026000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>28706000</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4675,8 +4835,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4749,8 +4910,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4823,8 +4987,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4897,8 +5064,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4971,82 +5141,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>157843000</v>
+      </c>
+      <c r="E72" s="3">
         <v>144647000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>121179000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>101577000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>106345000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>101326000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>102506000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>84972000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>81188000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>76793000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>82070000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>75205000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>67980000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>61241000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>64799000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>67056000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>69249000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>67712000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>69761000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>79233000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>85097000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>82343000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>77345000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>68513000</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5119,8 +5295,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5193,8 +5372,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5267,82 +5449,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>261221000</v>
+      </c>
+      <c r="E76" s="3">
         <v>243681000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>217243000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>194066000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>195070000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>185029000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>182637000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>164529000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>156763000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>149529000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>153168000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>142873000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>134033000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>124795000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>125713000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>124094000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>125767000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>123228000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>124879000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>133360000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>138227000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>133657000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>128290000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>117731000</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5415,161 +5603,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15848000</v>
+      </c>
+      <c r="E81" s="3">
         <v>26773000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>22768000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2709000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>18337000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16644000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>20838000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15688000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>13465000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>12369000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>14017000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11583000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7788000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5709000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4653000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4395000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6687000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7465000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>10285000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>9194000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>10394000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>9497000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>11219000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>7846000</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5596,82 +5793,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4342000</v>
+      </c>
+      <c r="E83" s="3">
         <v>3900000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4402000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3869000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3637000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3374000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3011000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2859000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2623000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2524000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2329000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2130000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1926000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2116000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2376000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2175000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1979000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2156000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2014000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1995000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1986000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1972000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1863000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1698000</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5744,8 +5945,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5818,8 +6022,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5892,8 +6099,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5966,8 +6176,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6040,82 +6253,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>31862000</v>
+      </c>
+      <c r="E89" s="3">
         <v>32226000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>36214000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>29999000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>25561000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>24026000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>27988000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>24724000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>19370000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>19246000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>19404000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>20402000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>17309000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>13998000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>14511000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9692000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>12196000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>14076000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>18104000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>14090000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>13247000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>12242000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>14040000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>9829000</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6142,82 +6361,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-30116000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18997000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-21383000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-18829000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16538000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12941000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-14425000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8258000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8173000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6400000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7592000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6496000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6134000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6823000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9043000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-9375000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7572000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5441000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5369000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4314000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4612000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4272000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4613000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3689000</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6290,8 +6513,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6364,82 +6590,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-49653000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-33678000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-34187000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21848000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-25958000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-20010000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-21498000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8620000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8298000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8734000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6472000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6077000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5203000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6743000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7531000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9701000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6959000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4779000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>5829000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-330000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-8195000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4874000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5173000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-16599000</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6466,40 +6698,41 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1353000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1346000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1338000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1330000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1327000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1329000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1270000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1263000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1266000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>1273000</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>10</v>
@@ -6510,8 +6743,8 @@
       <c r="P96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6540,8 +6773,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6614,8 +6850,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6688,8 +6927,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6762,226 +7004,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15967000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6553000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>25149000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10047000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-15977000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-19495000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5465000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4371000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11178000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-19767000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8401000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5875000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5292000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-10516000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7060000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2147000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6563000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-10660000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-21742000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-15252000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-8549000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5185000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3207000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2911000</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E101" s="3">
         <v>112000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-714000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>368000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-152000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-288000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>396000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-354000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-14000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>85000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>425000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-365000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-549000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-149000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>425000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-365000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-549000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-149000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-130000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-215000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>117000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-246000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>315000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>91000</v>
       </c>
     </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1831000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7998000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>27159000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1887000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16243000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15367000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>311000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>12101000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-258000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9543000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4927000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8096000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17384000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3176000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>345000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1773000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1875000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1512000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2061000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1707000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3380000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1937000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5975000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-9590000</v>
       </c>
     </row>
